--- a/public/templates/dryer-report-template.xlsx
+++ b/public/templates/dryer-report-template.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Bin No</t>
   </si>
@@ -106,28 +106,13 @@
   </si>
   <si>
     <t>DRYING MONITORING REPORT</t>
-  </si>
-  <si>
-    <t>=Date/Time Stop-Date/Time Start</t>
-  </si>
-  <si>
-    <t>=MC End-MC Start</t>
-  </si>
-  <si>
-    <t>= Total Drying/Dry Down</t>
-  </si>
-  <si>
-    <t>DOWNLOAD</t>
-  </si>
-  <si>
-    <t>PRINT PDF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,12 +140,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -210,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -222,24 +201,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:O51"/>
+  <dimension ref="B2:L51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -562,34 +536,30 @@
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" ht="23.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="7" t="s">
+    <row r="2" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="C2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="4" spans="2:12" ht="23.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="6" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>0</v>
       </c>
@@ -608,26 +578,20 @@
       <c r="G6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="J6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="L6" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -646,26 +610,20 @@
       <c r="G7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="J7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="L7" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
@@ -684,55 +642,49 @@
       <c r="G8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="L8" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10" t="s">
+      <c r="F10" s="5"/>
+      <c r="G10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="9" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
@@ -745,11 +697,11 @@
       <c r="H11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -758,10 +710,10 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -770,10 +722,10 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -782,10 +734,10 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -794,10 +746,10 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="2:15" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -806,8 +758,8 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -818,8 +770,8 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
@@ -830,8 +782,8 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
@@ -842,8 +794,8 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
@@ -854,8 +806,8 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
@@ -866,8 +818,8 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
@@ -878,8 +830,8 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
     </row>
     <row r="23" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
@@ -890,8 +842,8 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
     </row>
     <row r="24" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
@@ -902,8 +854,8 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
     </row>
     <row r="25" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
@@ -914,8 +866,8 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
@@ -926,8 +878,8 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
@@ -938,8 +890,8 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
     </row>
     <row r="28" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B28" s="1"/>
@@ -950,8 +902,8 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
     </row>
     <row r="29" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
@@ -962,8 +914,8 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
     </row>
     <row r="30" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B30" s="1"/>
@@ -974,8 +926,8 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
     </row>
     <row r="31" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B31" s="1"/>
@@ -986,8 +938,8 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
     </row>
     <row r="32" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B32" s="1"/>
@@ -998,8 +950,8 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
@@ -1010,8 +962,8 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
@@ -1022,8 +974,8 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
@@ -1034,8 +986,8 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
@@ -1046,8 +998,8 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
@@ -1058,8 +1010,8 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
@@ -1070,8 +1022,8 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
@@ -1082,8 +1034,8 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
@@ -1094,8 +1046,8 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
@@ -1106,8 +1058,8 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
@@ -1118,8 +1070,8 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
@@ -1130,8 +1082,8 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
@@ -1142,8 +1094,8 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
@@ -1154,8 +1106,8 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
@@ -1166,8 +1118,8 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
@@ -1178,8 +1130,8 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
@@ -1190,8 +1142,8 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
@@ -1202,8 +1154,8 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
@@ -1214,8 +1166,8 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
@@ -1226,43 +1178,11 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="J10:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="J50:K50"/>
     <mergeCell ref="J51:K51"/>
@@ -1279,6 +1199,38 @@
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J10:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/public/templates/dryer-report-template.xlsx
+++ b/public/templates/dryer-report-template.xlsx
@@ -201,6 +201,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -213,7 +214,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,33 +531,33 @@
   <dimension ref="B2:L51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
-      <c r="C2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="4" spans="2:12" ht="23.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -656,35 +656,35 @@
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
@@ -697,9 +697,9 @@
       <c r="H11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
@@ -710,8 +710,8 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
@@ -722,8 +722,8 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
@@ -734,8 +734,8 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
@@ -746,8 +746,8 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
@@ -758,8 +758,8 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
@@ -770,8 +770,8 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
@@ -782,8 +782,8 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
@@ -794,8 +794,8 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
@@ -806,8 +806,8 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
     </row>
     <row r="21" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
@@ -818,8 +818,8 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
@@ -830,8 +830,8 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
     </row>
     <row r="23" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
@@ -842,8 +842,8 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
     </row>
     <row r="24" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
@@ -854,8 +854,8 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
     </row>
     <row r="25" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
@@ -866,8 +866,8 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
@@ -878,10 +878,10 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -890,10 +890,10 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -902,10 +902,10 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -914,10 +914,10 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -926,10 +926,10 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -938,10 +938,10 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -950,8 +950,8 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
@@ -962,8 +962,8 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
@@ -974,8 +974,8 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
@@ -986,8 +986,8 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
@@ -998,8 +998,8 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
@@ -1010,8 +1010,8 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
@@ -1022,8 +1022,8 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
@@ -1034,8 +1034,8 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
@@ -1046,8 +1046,8 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
@@ -1058,8 +1058,8 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
@@ -1070,8 +1070,8 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
@@ -1082,8 +1082,8 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
@@ -1094,8 +1094,8 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
@@ -1106,8 +1106,8 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
@@ -1118,8 +1118,8 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
@@ -1130,8 +1130,8 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
@@ -1142,8 +1142,8 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
@@ -1154,8 +1154,8 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
@@ -1166,8 +1166,8 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
@@ -1178,8 +1178,8 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="48">

--- a/public/templates/dryer-report-template.xlsx
+++ b/public/templates/dryer-report-template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Bin No</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>MC (%)</t>
-  </si>
-  <si>
-    <t>Remaks</t>
   </si>
   <si>
     <t>DRYING MONITORING REPORT</t>
@@ -189,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -207,9 +204,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -229,6 +223,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>21811</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44610</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="523875"/>
+          <a:ext cx="1079086" cy="377985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -546,18 +583,18 @@
       <c r="J2" s="5"/>
     </row>
     <row r="4" spans="2:12" ht="23.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -676,10 +713,6 @@
       <c r="I10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
@@ -698,10 +731,8 @@
         <v>18</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -710,10 +741,8 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -722,10 +751,8 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -734,10 +761,8 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -746,10 +771,8 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="2:12" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -758,10 +781,8 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -770,10 +791,8 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -782,10 +801,8 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -794,10 +811,8 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -806,10 +821,8 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -818,10 +831,8 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -830,10 +841,8 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -842,10 +851,8 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-    </row>
-    <row r="24" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -854,10 +861,8 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -866,10 +871,8 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="2:11" ht="14.45" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -878,10 +881,8 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -890,10 +891,8 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -902,10 +901,8 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -914,10 +911,8 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -926,10 +921,8 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -938,10 +931,8 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -950,10 +941,8 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -962,10 +951,8 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -974,10 +961,8 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -986,10 +971,8 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -998,10 +981,8 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -1010,10 +991,8 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -1022,10 +1001,8 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -1034,10 +1011,8 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -1046,10 +1021,8 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -1058,10 +1031,8 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -1070,10 +1041,8 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -1082,10 +1051,8 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -1094,10 +1061,8 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -1106,10 +1071,8 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -1118,10 +1081,8 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -1130,10 +1091,8 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -1142,10 +1101,8 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -1154,10 +1111,8 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -1166,10 +1121,8 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -1178,53 +1131,10 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J51:K51"/>
+  <mergeCells count="7">
     <mergeCell ref="B4:K4"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J10:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
@@ -1234,5 +1144,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>